--- a/data/trans_dic/P25A$rendimiento-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P25A$rendimiento-Clase-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo para dejar de fumar fue, al menos, la disminución del rendimiento</t>
+          <t>Población cuyo motivo para dejar de fumar fue, al menos, la disminución del rendimiento (tasa de respuesta: 91,51%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,73</t>
+          <t>0,0; 6,98</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,48</t>
+          <t>0,0; 6,04</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,94; 15,4</t>
+          <t>2,86; 17,69</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,58; 24,09</t>
+          <t>2,59; 23,43</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,95; 17,17</t>
+          <t>1,91; 17,32</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,79; 15,24</t>
+          <t>1,68; 14,53</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,05; 9,46</t>
+          <t>1,57; 9,1</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,24; 7,45</t>
+          <t>1,23; 7,26</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,5; 12,27</t>
+          <t>3,49; 12,4</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,87</t>
+          <t>0,0; 6,79</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,32; 13,64</t>
+          <t>2,38; 13,97</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,31; 11,26</t>
+          <t>1,35; 11,81</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,21</t>
+          <t>0,0; 10,3</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,02</t>
+          <t>0,0; 8,79</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,74</t>
+          <t>0,0; 8,36</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,08</t>
+          <t>0,0; 5,41</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,04; 9,21</t>
+          <t>2,04; 9,72</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,76; 6,92</t>
+          <t>0,77; 7,46</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,88; 10,91</t>
+          <t>2,52; 10,88</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,85; 9,12</t>
+          <t>1,85; 9,19</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,91; 11,52</t>
+          <t>1,9; 11,34</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,56; 32,37</t>
+          <t>3,52; 30,85</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 5,78</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 13,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,3; 11,62</t>
+          <t>3,22; 12,34</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,52; 7,71</t>
+          <t>1,51; 7,64</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,65; 10,43</t>
+          <t>1,66; 10,18</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,41; 5,79</t>
+          <t>1,4; 5,53</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,58; 5,45</t>
+          <t>1,57; 5,31</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,06; 7,76</t>
+          <t>2,11; 7,4</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,47; 12,57</t>
+          <t>1,45; 12,34</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,86; 9,72</t>
+          <t>0,84; 9,31</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,32; 12,79</t>
+          <t>2,31; 13,1</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,8; 5,75</t>
+          <t>1,96; 5,99</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,69; 5,25</t>
+          <t>1,8; 5,49</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,91; 7,87</t>
+          <t>2,98; 7,66</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,0</t>
+          <t>0,0; 9,97</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,8; 8,48</t>
+          <t>0,89; 8,94</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,68; 10,86</t>
+          <t>1,78; 10,79</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0; 5,3</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,82</t>
+          <t>0,0; 12,06</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,32; 12,49</t>
+          <t>1,31; 13,71</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,59</t>
+          <t>0,0; 5,96</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,3; 7,46</t>
+          <t>1,27; 7,77</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,69; 9,15</t>
+          <t>2,65; 9,05</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 68,67</t>
+          <t>0,0; 68,77</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 65,99</t>
+          <t>0,0; 65,34</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,92</t>
+          <t>0,0; 12,0</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,43</t>
+          <t>0,0; 7,37</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,01</t>
+          <t>0,0; 19,39</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,66; 14,05</t>
+          <t>1,72; 15,9</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,37</t>
+          <t>0,0; 9,57</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,85</t>
+          <t>0,0; 17,14</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,97; 4,83</t>
+          <t>2,11; 4,83</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,44; 5,24</t>
+          <t>2,54; 5,32</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,62; 7,42</t>
+          <t>3,39; 7,18</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,93; 8,42</t>
+          <t>2,77; 8,7</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,55; 5,41</t>
+          <t>1,64; 5,56</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,93; 7,74</t>
+          <t>2,92; 7,39</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,6; 4,98</t>
+          <t>2,63; 4,99</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,58; 4,74</t>
+          <t>2,6; 4,8</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,73; 6,62</t>
+          <t>3,74; 6,47</t>
         </is>
       </c>
     </row>
@@ -1432,7 +1432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo para dejar de fumar fue, al menos, la disminución del rendimiento</t>
+          <t>Población cuyo motivo para dejar de fumar fue, al menos, la disminución del rendimiento (tasa de respuesta: 91,51%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1639,47 +1639,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 6449</t>
+          <t>0; 6697</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 6143</t>
+          <t>0; 6773</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2747; 14378</t>
+          <t>2675; 16510</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>981; 9170</t>
+          <t>985; 8919</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1008; 8877</t>
+          <t>988; 8951</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1099; 9355</t>
+          <t>1033; 8919</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2742; 12665</t>
+          <t>2103; 12192</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2027; 12200</t>
+          <t>2014; 11897</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>5413; 18985</t>
+          <t>5406; 19190</t>
         </is>
       </c>
     </row>
@@ -1802,47 +1802,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 5483</t>
+          <t>0; 5422</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2089; 12266</t>
+          <t>2137; 12563</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>955; 8202</t>
+          <t>984; 8607</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 4130</t>
+          <t>0; 4167</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 4333</t>
+          <t>0; 4754</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 5183</t>
+          <t>0; 5598</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 6108</t>
+          <t>0; 6514</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2943; 13258</t>
+          <t>2933; 13996</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1058; 9668</t>
+          <t>1072; 10423</t>
         </is>
       </c>
     </row>
@@ -1965,47 +1965,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2011; 11645</t>
+          <t>2686; 11610</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2990; 14779</t>
+          <t>2999; 14879</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1879; 11323</t>
+          <t>1865; 11143</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>868; 7892</t>
+          <t>859; 7520</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 2033</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 1779</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4328; 15230</t>
+          <t>4224; 16181</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2998; 15208</t>
+          <t>2973; 15063</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1844; 11623</t>
+          <t>1852; 11349</t>
         </is>
       </c>
     </row>
@@ -2128,47 +2128,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3850; 15764</t>
+          <t>3800; 15055</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5042; 17371</t>
+          <t>5002; 16925</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4691; 17678</t>
+          <t>4802; 16855</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>931; 7964</t>
+          <t>919; 7816</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>978; 10998</t>
+          <t>947; 10537</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2014; 11082</t>
+          <t>2001; 11354</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6033; 19276</t>
+          <t>6563; 20107</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>7286; 22670</t>
+          <t>7776; 23735</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>9141; 24735</t>
+          <t>9378; 24082</t>
         </is>
       </c>
     </row>
@@ -2291,47 +2291,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 6357</t>
+          <t>0; 6342</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1011; 10786</t>
+          <t>1138; 11369</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1808; 11696</t>
+          <t>1913; 11620</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 1882</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 8209</t>
+          <t>0; 8377</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>929; 8766</t>
+          <t>922; 9622</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 6534</t>
+          <t>0; 5901</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>2564; 14662</t>
+          <t>2492; 15272</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>4777; 16276</t>
+          <t>4722; 16091</t>
         </is>
       </c>
     </row>
@@ -2454,47 +2454,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 3795</t>
+          <t>0; 3801</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 3970</t>
+          <t>0; 3931</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 1703</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 5837</t>
+          <t>0; 5877</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 4527</t>
+          <t>0; 4494</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 6871</t>
+          <t>0; 7007</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>907; 7658</t>
+          <t>940; 8670</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 6941</t>
+          <t>0; 6406</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 7443</t>
+          <t>0; 7147</t>
         </is>
       </c>
     </row>
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>12303; 30150</t>
+          <t>13152; 30131</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>19923; 42768</t>
+          <t>20728; 43390</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>21916; 44924</t>
+          <t>20534; 43484</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>7348; 21121</t>
+          <t>6940; 21806</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>5976; 20811</t>
+          <t>6296; 21382</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>9789; 25882</t>
+          <t>9776; 24724</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>22701; 43528</t>
+          <t>22992; 43655</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>31031; 56901</t>
+          <t>31239; 57654</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>35104; 62235</t>
+          <t>35133; 60838</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P25A$rendimiento-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P25A$rendimiento-Clase-trans_dic.xlsx
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,98</t>
+          <t>0,0; 6,82</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,04</t>
+          <t>0,0; 6,12</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,86; 17,69</t>
+          <t>2,96; 16,63</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,59; 23,43</t>
+          <t>2,51; 23,77</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,91; 17,32</t>
+          <t>1,87; 16,33</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,68; 14,53</t>
+          <t>1,74; 15,24</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,57; 9,1</t>
+          <t>1,59; 9,17</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,23; 7,26</t>
+          <t>1,25; 7,73</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,49; 12,4</t>
+          <t>3,59; 12,62</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,79</t>
+          <t>0,0; 6,4</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,38; 13,97</t>
+          <t>2,32; 13,15</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,35; 11,81</t>
+          <t>1,34; 11,54</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,3</t>
+          <t>0,0; 10,35</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,79</t>
+          <t>0,0; 10,15</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,36</t>
+          <t>0,0; 6,57</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,41</t>
+          <t>0,0; 4,8</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,04; 9,72</t>
+          <t>2,03; 9,73</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,77; 7,46</t>
+          <t>0,77; 7,02</t>
         </is>
       </c>
     </row>
@@ -898,22 +898,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,52; 10,88</t>
+          <t>1,78; 10,47</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,85; 9,19</t>
+          <t>1,86; 9,31</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,9; 11,34</t>
+          <t>1,83; 11,31</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,52; 30,85</t>
+          <t>3,57; 32,84</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -928,17 +928,17 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,22; 12,34</t>
+          <t>3,22; 13,01</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,51; 7,64</t>
+          <t>1,51; 7,61</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,66; 10,18</t>
+          <t>1,7; 10,22</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,4; 5,53</t>
+          <t>1,45; 5,71</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,57; 5,31</t>
+          <t>1,52; 5,35</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,11; 7,4</t>
+          <t>2,17; 8,06</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,45; 12,34</t>
+          <t>1,45; 12,29</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,84; 9,31</t>
+          <t>0,87; 9,27</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,31; 13,1</t>
+          <t>2,17; 12,34</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,96; 5,99</t>
+          <t>1,71; 5,6</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,8; 5,49</t>
+          <t>1,79; 5,62</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,98; 7,66</t>
+          <t>2,66; 7,51</t>
         </is>
       </c>
     </row>
@@ -1118,17 +1118,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,97</t>
+          <t>0,0; 10,6</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,89; 8,94</t>
+          <t>0,91; 8,78</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,78; 10,79</t>
+          <t>1,74; 11,1</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1138,34 +1138,34 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,06</t>
+          <t>0,0; 10,67</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,31; 13,71</t>
+          <t>1,49; 12,56</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,96</t>
+          <t>0,0; 6,83</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,27; 7,77</t>
+          <t>1,42; 7,62</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,65; 9,05</t>
+          <t>2,72; 9,29</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 68,77</t>
+          <t>0,0; 69,16</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 65,34</t>
+          <t>0,0; 57,07</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1243,32 +1243,32 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,0</t>
+          <t>0,0; 11,76</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,37</t>
+          <t>0,0; 9,08</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,39</t>
+          <t>0,0; 19,55</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,72; 15,9</t>
+          <t>1,72; 17,37</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,57</t>
+          <t>0,0; 10,59</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,14</t>
+          <t>0,0; 17,01</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,11; 4,83</t>
+          <t>2,13; 4,98</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,54; 5,32</t>
+          <t>2,63; 5,33</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,39; 7,18</t>
+          <t>3,42; 7,01</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,77; 8,7</t>
+          <t>2,81; 8,19</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,64; 5,56</t>
+          <t>1,64; 5,85</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,92; 7,39</t>
+          <t>2,97; 7,64</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,63; 4,99</t>
+          <t>2,63; 5,1</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,6; 4,8</t>
+          <t>2,64; 4,96</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,74; 6,47</t>
+          <t>3,55; 6,67</t>
         </is>
       </c>
     </row>
@@ -1639,47 +1639,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 6697</t>
+          <t>0; 6537</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 6773</t>
+          <t>0; 6856</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2675; 16510</t>
+          <t>2761; 15527</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>985; 8919</t>
+          <t>954; 9050</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>988; 8951</t>
+          <t>968; 8444</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1033; 8919</t>
+          <t>1068; 9354</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2103; 12192</t>
+          <t>2128; 12281</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2014; 11897</t>
+          <t>2055; 12658</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>5406; 19190</t>
+          <t>5554; 19523</t>
         </is>
       </c>
     </row>
@@ -1802,47 +1802,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 5422</t>
+          <t>0; 5114</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2137; 12563</t>
+          <t>2086; 11825</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>984; 8607</t>
+          <t>974; 8405</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 4167</t>
+          <t>0; 4190</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 4754</t>
+          <t>0; 5485</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 5598</t>
+          <t>0; 4396</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 6514</t>
+          <t>0; 5771</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2933; 13996</t>
+          <t>2929; 14002</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1072; 10423</t>
+          <t>1075; 9810</t>
         </is>
       </c>
     </row>
@@ -1965,22 +1965,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2686; 11610</t>
+          <t>1904; 11167</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2999; 14879</t>
+          <t>3010; 15079</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1865; 11143</t>
+          <t>1798; 11113</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>859; 7520</t>
+          <t>870; 8004</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1995,17 +1995,17 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4224; 16181</t>
+          <t>4223; 17050</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2973; 15063</t>
+          <t>2985; 15007</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1852; 11349</t>
+          <t>1893; 11390</t>
         </is>
       </c>
     </row>
@@ -2128,47 +2128,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3800; 15055</t>
+          <t>3954; 15536</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5002; 16925</t>
+          <t>4855; 17060</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4802; 16855</t>
+          <t>4949; 18356</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>919; 7816</t>
+          <t>921; 7784</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>947; 10537</t>
+          <t>979; 10494</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2001; 11354</t>
+          <t>1881; 10692</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6563; 20107</t>
+          <t>5735; 18779</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>7776; 23735</t>
+          <t>7727; 24298</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>9378; 24082</t>
+          <t>8378; 23604</t>
         </is>
       </c>
     </row>
@@ -2291,17 +2291,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 6342</t>
+          <t>0; 6743</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1138; 11369</t>
+          <t>1155; 11167</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1913; 11620</t>
+          <t>1876; 11957</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -2311,34 +2311,34 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 8377</t>
+          <t>0; 7409</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>922; 9622</t>
+          <t>1046; 8818</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 5901</t>
+          <t>0; 6769</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>2492; 15272</t>
+          <t>2787; 14984</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>4722; 16091</t>
+          <t>4838; 16527</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2454,12 +2454,12 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 3801</t>
+          <t>0; 3823</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 3931</t>
+          <t>0; 3433</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -2469,32 +2469,32 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 5877</t>
+          <t>0; 5762</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 4494</t>
+          <t>0; 5535</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 7007</t>
+          <t>0; 7064</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>940; 8670</t>
+          <t>939; 9467</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 6406</t>
+          <t>0; 7090</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 7147</t>
+          <t>0; 7095</t>
         </is>
       </c>
     </row>
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>13152; 30131</t>
+          <t>13261; 31054</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>20728; 43390</t>
+          <t>21455; 43465</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>20534; 43484</t>
+          <t>20699; 42437</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>6940; 21806</t>
+          <t>7051; 20533</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>6296; 21382</t>
+          <t>6308; 22476</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>9776; 24724</t>
+          <t>9945; 25558</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>22992; 43655</t>
+          <t>23011; 44604</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>31239; 57654</t>
+          <t>31655; 59596</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>35133; 60838</t>
+          <t>33339; 62738</t>
         </is>
       </c>
     </row>
